--- a/Resultados/- Hash Convencional.xlsx
+++ b/Resultados/- Hash Convencional.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\Resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CD1AAD-CBD9-465D-9171-E167CA76D63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A0F003-4D66-4613-B5C5-0F49E6963F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="20" r:id="rId1"/>
     <sheet name="MountainDatabase" sheetId="22" r:id="rId2"/>
     <sheet name="PalaceDatabase" sheetId="23" r:id="rId3"/>
     <sheet name="WashingtonDatabase" sheetId="21" r:id="rId4"/>
+    <sheet name="ParkDatabase" sheetId="24" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="358">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -753,6 +754,366 @@
   </si>
   <si>
     <t>558ee9100bcc7cbf755d46f18f0c6b6159bc3199e69b634702bc3b8b91293239</t>
+  </si>
+  <si>
+    <t>3e91b66e400324c267c458341ea99cdf</t>
+  </si>
+  <si>
+    <t>783d4f5889ce60d6aa815ef98ebd75fff7d85c05</t>
+  </si>
+  <si>
+    <t>6832e6d9972c812633249e5c1b135864309e4b7fdf227d85d600ac095e1e04ee</t>
+  </si>
+  <si>
+    <t>9f5469b8bb4534e4424cacf2fe26a934</t>
+  </si>
+  <si>
+    <t>004dc2d7187717c5ee07d32e929eb25e6759422d</t>
+  </si>
+  <si>
+    <t>8848e931892e4f09ab3073ee3e7d64b36fd842ea2f5f5abb6ce2493d7ac974f3</t>
+  </si>
+  <si>
+    <t>00b83141b9b87b9d3cd57b59ce85edf4</t>
+  </si>
+  <si>
+    <t>8e30789fd0026ccf23c67ec7e982f476752372f6</t>
+  </si>
+  <si>
+    <t>433aaf9e5374618b3f31f55b65182eb18804c6bc7af55e268c2d49874dde08a9</t>
+  </si>
+  <si>
+    <t>c9e17a50b325af38b3cf9e9a109e52d6</t>
+  </si>
+  <si>
+    <t>af02e8977041f536dfe3e235a0cdd9d7f0f806f0</t>
+  </si>
+  <si>
+    <t>cc6b51597bc9a22ea4aae2ffae1cf7ba51791a4e32b18a93360b30a094ae56e1</t>
+  </si>
+  <si>
+    <t>1a7fd642824a7ba326c59de397934f50</t>
+  </si>
+  <si>
+    <t>483f8b6dde283831791ad719e2cc53d473b662a7</t>
+  </si>
+  <si>
+    <t>5e0cace8927bc93e6a90bc0a8d544bc57e10ec9e7fdbad99090f854791c55566</t>
+  </si>
+  <si>
+    <t>4ba7b677e2dbc0caeffb9ff1f3dfde50</t>
+  </si>
+  <si>
+    <t>9f86395b79752575974c6eacc27e11aa791ae66e</t>
+  </si>
+  <si>
+    <t>76a260eda89735644dd0a57feaaecd214f1795f6e33bce18ce4dd805b614ec6d</t>
+  </si>
+  <si>
+    <t>b6695f0bbcabd53212cbad39abcc462b</t>
+  </si>
+  <si>
+    <t>0aeb4c668177da3c8978935b69c150d03be3076c</t>
+  </si>
+  <si>
+    <t>f70c87dc78ebfec9fa47ceb99d085d103da7542b1ac96ad06755fc9fdefdbfcf</t>
+  </si>
+  <si>
+    <t>41c798938e72700527d9d9a073b8af48</t>
+  </si>
+  <si>
+    <t>597351cb04fecbacba2567a4abf84ae82aed51af</t>
+  </si>
+  <si>
+    <t>2d8c170a6b5eceb55f1fded124a69d4252da3e7a7fa0eadc111d82719a86e43c</t>
+  </si>
+  <si>
+    <t>07e1a434fc758e1cc31a7b355afa71b2</t>
+  </si>
+  <si>
+    <t>e50b1c0203b935948e06768c7350c311e3b93b24</t>
+  </si>
+  <si>
+    <t>00b640daf352d0496f02be91e8f0e2ee2e2be543c026c9d306159f6da1f8cf84</t>
+  </si>
+  <si>
+    <t>59bbe5e8cfb91e97a6eb8ab86920dd7b</t>
+  </si>
+  <si>
+    <t>fd97f90554778993220cfae38921e8fcf09a0717</t>
+  </si>
+  <si>
+    <t>7d6f49968cfbe4a9909ba9d7a50b1ec9a2fe752d6b5d71381e509bfcd98b490e</t>
+  </si>
+  <si>
+    <t>f5399670df1924933a674b7db17547dd</t>
+  </si>
+  <si>
+    <t>2a0ccfc0018b5fc6ef4d59b2b2572c62ddac4385</t>
+  </si>
+  <si>
+    <t>43ab023910913fa15f3995399b4130235ccad220a6684468f4d1483799464954</t>
+  </si>
+  <si>
+    <t>5967f12a3041a3e472bf83249c0bbe41</t>
+  </si>
+  <si>
+    <t>4c4cb1d3ae01b35ce5f0c93d5499252b92df34b1</t>
+  </si>
+  <si>
+    <t>e3cc06ec914de6f7bd5c8316be662cf6cf6020b30848a528536107c1498b0f13</t>
+  </si>
+  <si>
+    <t>be560fb39acbea10814bf00cba190e5e</t>
+  </si>
+  <si>
+    <t>63007c46824521f5fc78740797b6f52266f1b3bb</t>
+  </si>
+  <si>
+    <t>f6dd8320db2f2463337d1f90fa60156fcdbf4200d3b060513fe34b98e81ea4ab</t>
+  </si>
+  <si>
+    <t>c39c24a41d1e44183e545b8c6bc75950</t>
+  </si>
+  <si>
+    <t>0458f02b050e90ae526887328026b8b6addced46</t>
+  </si>
+  <si>
+    <t>d628f0cbd8c8858d0b1ce393489eb352e645c23ada2b696c445a0a3d42251962</t>
+  </si>
+  <si>
+    <t>43eddb8c32c35ffc60264914602101db</t>
+  </si>
+  <si>
+    <t>a823e59e0bacaf392d7396534c81b1dc47e1bf45</t>
+  </si>
+  <si>
+    <t>4abe8eb1ac9baa806a63509869750aef97b0b44c3bc8b816fbdbf6465bcd62f3</t>
+  </si>
+  <si>
+    <t>b6315871e72caa1e637d76c27d29f0ae</t>
+  </si>
+  <si>
+    <t>ac9433317eeea07f8a40e9a3975ee806d640a247</t>
+  </si>
+  <si>
+    <t>5a20b12528d0e688525eeb2f3fc294f0fdcab8b386c244e7b5d73fa24b4569b5</t>
+  </si>
+  <si>
+    <t>861c217294bd410fbcf2339971240d86</t>
+  </si>
+  <si>
+    <t>e35112ff9fa3a46fbe6833a459bb314e4e97126d</t>
+  </si>
+  <si>
+    <t>e44af0db6640449ee1403194ade0e4c0f0d47d5fa79f9627a49f6e978f20f802</t>
+  </si>
+  <si>
+    <t>be54c4f3b8ebdfade00a24945052a8ab</t>
+  </si>
+  <si>
+    <t>f1a231d6f7d90107cfc518e9157bb108c64ee184</t>
+  </si>
+  <si>
+    <t>05819209f8f44509a15fb57c50b13f1fd70936c4da8d1caf2674861c9c191117</t>
+  </si>
+  <si>
+    <t>a2e7be78c569ca49f44571412df67ea5</t>
+  </si>
+  <si>
+    <t>08b4d6ac3496ccab68d2252e0e5618e400822a56</t>
+  </si>
+  <si>
+    <t>b6017b66dfcc2694ba0cd7a741266634aa9e6713660fbdba397df834409decd3</t>
+  </si>
+  <si>
+    <t>695a9083f7863fff4613c828699caf0b</t>
+  </si>
+  <si>
+    <t>23307ab7dd79ad32698b84da1dc13b146d3583bb</t>
+  </si>
+  <si>
+    <t>7ced9431d9b7cde95dbf159f864e5286848f5a64518b624d29db3005b03d3082</t>
+  </si>
+  <si>
+    <t>312e70ad2c2e444154a537f0a787b5e7</t>
+  </si>
+  <si>
+    <t>dd2e3a99b44d58dd11d27a1a5c5762f898e123ba</t>
+  </si>
+  <si>
+    <t>9cc57f099267a575669edcd968e8fa06294eb19a49bc5fa34c399ff3066e9a0a</t>
+  </si>
+  <si>
+    <t>e199098c7686c726530cf8b9899e006c</t>
+  </si>
+  <si>
+    <t>8ea9e0c1e83c3b8706695cde470995e1c2d31a37</t>
+  </si>
+  <si>
+    <t>fabb189b1d4a51d2179efffa74cf84984fd0403e543224baf411c5a5762c3424</t>
+  </si>
+  <si>
+    <t>c12dedd7b2c47d30080658918b930c61</t>
+  </si>
+  <si>
+    <t>d08a94f57724d41af3aa6fcda354aaa13e9c5c55</t>
+  </si>
+  <si>
+    <t>75e179a6ac554383ae20ae43ebc19125ad3876ad73f4a96c7b7211be1df975ca</t>
+  </si>
+  <si>
+    <t>e8fc3d05c638498c0a0c3df995d9855a</t>
+  </si>
+  <si>
+    <t>3b677f9b80a5a1210b8f37766f142e837013192f</t>
+  </si>
+  <si>
+    <t>b71ea2b74b6953c638018fa3e62d3391d3d671ae7f676eaa2a7cefe9a2bd2490</t>
+  </si>
+  <si>
+    <t>3ed4d87da03efa74fe0e391b265a7b3d</t>
+  </si>
+  <si>
+    <t>83f23d2381259e29440516237854f1e3dc8c9a5b</t>
+  </si>
+  <si>
+    <t>315df15475219b67fb93e3cc0b7991ab97fe165a96d0b60b2498c7ca6998488a</t>
+  </si>
+  <si>
+    <t>5d6d3bdf5bedfd7eb4e1864a665f8e57</t>
+  </si>
+  <si>
+    <t>2e1cc2c0c91506e714b3195b4dea0b3c4e665093</t>
+  </si>
+  <si>
+    <t>34966162b84e4568cf43dc92663d61b0030ad12241a9f5ae429ae8f8840e6e98</t>
+  </si>
+  <si>
+    <t>e96cc93e3f3d9693297493ac54cc4b72</t>
+  </si>
+  <si>
+    <t>67ab1b117a4426f8707430aa1f0576ded6adda3c</t>
+  </si>
+  <si>
+    <t>522f093a2ba4317a75cf8f073d364d224831896f4866b6d5af35a96f19682812</t>
+  </si>
+  <si>
+    <t>71faeeb5bab536d829e49e0d272f86e4</t>
+  </si>
+  <si>
+    <t>5fdf486e814d435fdc0b491db54f547df1700b68</t>
+  </si>
+  <si>
+    <t>ff2c71dabecd8c1047d7af70b8debfa2c133ccdc337fe85027c14f2d1e719aec</t>
+  </si>
+  <si>
+    <t>464ce339982fbd50abdc243695d250ab</t>
+  </si>
+  <si>
+    <t>61775d3270673ccaeaac93c9ce2f94a97f862aab</t>
+  </si>
+  <si>
+    <t>fe78922140d4f3edbb82cb8cedfd2e3bd8d42b634ac8ff4b6b6452ef74ad64e0</t>
+  </si>
+  <si>
+    <t>50bc149eb583e1259273d2eb6bd5af4f</t>
+  </si>
+  <si>
+    <t>37e8b6556357e2ab3b9948c9b4a775f083cf58b9</t>
+  </si>
+  <si>
+    <t>f924037cee44688d5baef599095847c8c8940f880ec9be6bd48f67da228f52c1</t>
+  </si>
+  <si>
+    <t>7866db0c95e7071ab2036ea2a267e71a</t>
+  </si>
+  <si>
+    <t>cc1a4258ccac083fac4eaf48c901a2256bda983e</t>
+  </si>
+  <si>
+    <t>9644576a4720911a52bcf2cb1304741a5f453efb2e12afd54bca55d5003512e9</t>
+  </si>
+  <si>
+    <t>dadfab3961d6fbbdfa496275823056d6</t>
+  </si>
+  <si>
+    <t>14ea037b889d9a25801226fd2e2422c58ac6ad62</t>
+  </si>
+  <si>
+    <t>35433375fb83c2938978e4ea72db1973582204d2dc2e79009e43a9e61b57231b</t>
+  </si>
+  <si>
+    <t>0e91219a00d30428fc02d2c933a267e4</t>
+  </si>
+  <si>
+    <t>4e33dd31c6d675ab5d535ebf9430475499e156ba</t>
+  </si>
+  <si>
+    <t>81fb3e670a8da97040bcec84793451bba79ca4e662363df4467a6fb892d630de</t>
+  </si>
+  <si>
+    <t>e712322fecde37b2a004c54e3dfcc48e</t>
+  </si>
+  <si>
+    <t>d2eb047e5c46fd3dceb8d0bb6605a4581e6d4733</t>
+  </si>
+  <si>
+    <t>98660f4d403df890dbc0d03d2abc05f781097ad33ffe5f9def230da774a8ce77</t>
+  </si>
+  <si>
+    <t>51726796e1482cb50f73df13abfbf95b</t>
+  </si>
+  <si>
+    <t>853eedd5a9fc93a1d87141037bfc23cbc007fa3d</t>
+  </si>
+  <si>
+    <t>0950f7cdf150fd3832dcafaf014c263b50d231c49adc0cc59c3f114033378171</t>
+  </si>
+  <si>
+    <t>bc6be94c1be85f929059c5c95018ec88</t>
+  </si>
+  <si>
+    <t>985a77037bd9155f591458ec3cbd686e29f59f31</t>
+  </si>
+  <si>
+    <t>79a4293770dab6e3177417d7250dd5517264277d13c0969f6ed4b8cf26fb4824</t>
+  </si>
+  <si>
+    <t>740d15b389739ed0892f85ae64ab7a59</t>
+  </si>
+  <si>
+    <t>7ac6331e7e7be02f21cf0b90345250df27419510</t>
+  </si>
+  <si>
+    <t>5c08f3826a813766b4f369dba8a0b5877c3c39855446a4880ef3cf3ac3aa31e9</t>
+  </si>
+  <si>
+    <t>e0fd10c5bfd5dd8459c2c9a4c9009b76</t>
+  </si>
+  <si>
+    <t>089e47c8e0c04eaf7a2e36e66fe9233fc1dfac0e</t>
+  </si>
+  <si>
+    <t>26aacc5635cc3caf4ea74d1ce621cbb860c331ce3a45549c7e03abdf5e78172a</t>
+  </si>
+  <si>
+    <t>c10ebb67584f07bd48eea30b81b3d089</t>
+  </si>
+  <si>
+    <t>654b2373f51956529e948e7dcaf07e7d35aa6475</t>
+  </si>
+  <si>
+    <t>77c2bf26e8ed839d999a2f843e510daefba6453a508088c56bd3db8fd950f5de</t>
+  </si>
+  <si>
+    <t>8b03a13327f2197a1c9b5eefb95b44ce</t>
+  </si>
+  <si>
+    <t>5fea5a260f73f39a3437a15894e7d6765c37d78d</t>
+  </si>
+  <si>
+    <t>eccf7229a28cc2678ead50dae8f5b4bf919a03826e8557cd8fd11a4d3ab186ce</t>
   </si>
 </sst>
 </file>
@@ -1977,233 +2338,407 @@
       <c r="A4" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="7"/>
+      <c r="B10" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="7"/>
+      <c r="B11" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="B16" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="B17" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
+      <c r="B18" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
+      <c r="B19" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+      <c r="B20" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
+      <c r="B21" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+      <c r="B22" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
+      <c r="B23" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
+      <c r="B24" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="B25" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
+      <c r="B26" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
+      <c r="B27" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
+      <c r="B28" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
+      <c r="B29" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
+      <c r="B30" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
+      <c r="B31" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
+      <c r="B32" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>324</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -2337,4 +2872,189 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D75A3B-19EA-4EE4-B1B4-A65D5ECA8177}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="67.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>